--- a/input/timetable/Магистратура_Пед.образ.xlsx
+++ b/input/timetable/Магистратура_Пед.образ.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D83AE0-43FD-45AD-9DC3-B96403122C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -14,12 +15,12 @@
     <definedName name="Группы">#REF!</definedName>
     <definedName name="Подписи">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="95">
   <si>
     <t>пара</t>
   </si>
@@ -72,6 +73,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -111,9 +115,24 @@
     <t>Практикум по межкультурной коммуникации (пр),ЭОиДОТ</t>
   </si>
   <si>
+    <t>Сальков А.В.</t>
+  </si>
+  <si>
+    <t>Богач М.А.</t>
+  </si>
+  <si>
+    <t>Варлакова Ю.Р.</t>
+  </si>
+  <si>
+    <t>Добрынина О.В.</t>
+  </si>
+  <si>
     <t>История и методология науки (пр), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Муллер О.Ю.</t>
+  </si>
+  <si>
     <t>Методология и дидактика STEAM (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -138,6 +157,9 @@
     <t>Научный семинар и исследовательская деятельность педагога профессионального образования (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Насырова Э.Ф./Усольцева И.В.</t>
+  </si>
+  <si>
     <t>Методика профессионального обучения (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -159,6 +181,9 @@
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ// Технологии сопровождения проектной деятельности в образовании (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Демчук А.В.</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
@@ -186,6 +211,18 @@
     <t>Технологии кросс-дисциплинарного проектирования в образовании (ТО: 02.02.2026-06.06.2026)</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Сальков А.В./Муллер О.Ю.</t>
+  </si>
+  <si>
+    <t>Дроздова А.А.</t>
+  </si>
+  <si>
+    <t>Повзун В.Д.</t>
+  </si>
+  <si>
     <t>Аксиология  образования  (лек), ЭОиДОТ</t>
   </si>
   <si>
@@ -234,15 +271,27 @@
     <t>Учебная практика, технологическая (проектно-технологическая) практика, ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Касьяненко-Божок Р.В.</t>
+  </si>
+  <si>
+    <t>Мойсеенкова М.А.</t>
+  </si>
+  <si>
     <t>Научный семинар и исследовательская деятельность педагога профессионального образования (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Насырова Э.Ф.</t>
+  </si>
+  <si>
     <t>Научный семинар и исследовательская деятельность педагога профессионального образования (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t>// Научный семинар и исследовательская деятельность педагога профессионального образования (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Иванова Е.А./Муллер О.Ю.</t>
+  </si>
+  <si>
     <t>Общая инженерная и компьютерная графика (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
@@ -253,12 +302,15 @@
   </si>
   <si>
     <t>Информационные технологии в образовании (пр), ЭОиДОТ//</t>
+  </si>
+  <si>
+    <t>ФТД: Психолого-педагогическое сопровождение одаренных детей в образовательном процессе (пр), ЭОиДОТ//</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -353,7 +405,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,12 +424,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -448,6 +506,64 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -937,7 +1053,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -973,28 +1089,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1003,6 +1122,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
@@ -1012,9 +1132,11 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1022,7 +1144,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1031,6 +1153,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1038,275 +1162,284 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="3"/>
-    <cellStyle name="Обычный 3" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Хороший" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1398,6 +1531,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1433,6 +1583,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1608,8 +1775,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1618,96 +1785,99 @@
     <col min="4" max="4" width="17.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="20" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="16.140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20" style="2" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="16.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.140625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="H2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="O2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="L4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="R4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="M4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="T4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1716,911 +1886,1041 @@
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="4" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="7"/>
+      <c r="O5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="6"/>
+      <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="7"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R5" s="6"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="7"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="J6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" s="11" t="s">
+      <c r="Q6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="R6" s="9"/>
+      <c r="S6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="35"/>
+      <c r="C7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="39"/>
       <c r="E7" s="10">
         <v>1</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="10">
+      <c r="J7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="39"/>
+      <c r="L7" s="10">
         <v>1</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="O7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="10">
+      <c r="Q7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="R7" s="39"/>
+      <c r="S7" s="10">
         <v>1</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="47" t="s">
+    <row r="8" spans="1:21" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="62"/>
       <c r="E8" s="13" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="47" t="s">
+      <c r="H8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="47"/>
-      <c r="K8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="14" t="s">
+      <c r="K8" s="62"/>
+      <c r="L8" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8" s="47" t="s">
+      <c r="O8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="14" t="s">
+      <c r="R8" s="62"/>
+      <c r="S8" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="T8" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-    </row>
-    <row r="10" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="H9" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="O9" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="R9" s="63"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="63"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="16" t="s">
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="J10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="J10" s="18"/>
       <c r="K10" s="19"/>
       <c r="L10" s="20"/>
-      <c r="M10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="16" t="s">
+      <c r="M10" s="21"/>
+      <c r="N10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="O10" s="17" t="s">
+      <c r="Q10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="R10" s="19"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23">
         <v>6</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="23">
+        <v>6</v>
+      </c>
+      <c r="J11" s="79"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="23">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="80"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="30"/>
+    </row>
+    <row r="12" spans="1:21" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
+        <v>7</v>
+      </c>
+      <c r="C12" s="67"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="25">
+        <v>7</v>
+      </c>
+      <c r="J12" s="82" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="24"/>
+      <c r="P12" s="25">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="R12" s="128"/>
+      <c r="S12" s="128"/>
+      <c r="T12" s="129"/>
+      <c r="U12" s="56" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
+        <v>8</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28">
+        <v>8</v>
+      </c>
+      <c r="J13" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O13" s="27"/>
+      <c r="P13" s="28">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="76" t="s">
+        <v>52</v>
+      </c>
+      <c r="R13" s="77"/>
+      <c r="S13" s="77"/>
+      <c r="T13" s="78"/>
+      <c r="U13" s="56" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="23">
+        <v>6</v>
+      </c>
+      <c r="C14" s="73"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="23">
+        <v>6</v>
+      </c>
+      <c r="J14" s="88"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" s="23">
+        <v>6</v>
+      </c>
+      <c r="Q14" s="88"/>
+      <c r="R14" s="89"/>
+      <c r="S14" s="89"/>
+      <c r="T14" s="90"/>
+      <c r="U14" s="30"/>
+    </row>
+    <row r="15" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
+        <v>7</v>
+      </c>
+      <c r="C15" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25">
+        <v>7</v>
+      </c>
+      <c r="J15" s="85" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="25">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="76" t="s">
+        <v>37</v>
+      </c>
+      <c r="R15" s="77"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="56" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="31"/>
+      <c r="B16" s="28">
+        <v>8</v>
+      </c>
+      <c r="C16" s="91" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="92"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="31"/>
+      <c r="I16" s="28">
+        <v>8</v>
+      </c>
+      <c r="J16" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="105"/>
+      <c r="N16" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="31"/>
+      <c r="P16" s="28">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="130"/>
+      <c r="R16" s="131"/>
+      <c r="S16" s="131"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="32"/>
+    </row>
+    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="23">
+        <v>6</v>
+      </c>
+      <c r="C17" s="94"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="23">
+        <v>6</v>
+      </c>
+      <c r="J17" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="107"/>
+      <c r="L17" s="107"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="23">
+        <v>6</v>
+      </c>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="110"/>
+      <c r="S17" s="110"/>
+      <c r="T17" s="111"/>
+      <c r="U17" s="30"/>
+    </row>
+    <row r="18" spans="1:21" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
+        <v>7</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="33"/>
+      <c r="I18" s="25">
+        <v>7</v>
+      </c>
+      <c r="J18" s="85"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="25">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="R18" s="77"/>
+      <c r="S18" s="77"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="31"/>
+      <c r="B19" s="28">
+        <v>8</v>
+      </c>
+      <c r="C19" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="31"/>
+      <c r="I19" s="28">
+        <v>8</v>
+      </c>
+      <c r="J19" s="103"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="105"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="28">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="R19" s="92"/>
+      <c r="S19" s="92"/>
+      <c r="T19" s="93"/>
+      <c r="U19" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="23">
+        <v>6</v>
+      </c>
+      <c r="C20" s="109"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
+        <v>6</v>
+      </c>
+      <c r="J20" s="109"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="23">
+        <v>6</v>
+      </c>
+      <c r="Q20" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="99"/>
+      <c r="U20" s="30"/>
+    </row>
+    <row r="21" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>7</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="24"/>
+      <c r="I21" s="25">
+        <v>7</v>
+      </c>
+      <c r="J21" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="77"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" s="24"/>
+      <c r="P21" s="25">
+        <v>7</v>
+      </c>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="134"/>
+      <c r="S21" s="134"/>
+      <c r="T21" s="135"/>
+      <c r="U21" s="26"/>
+    </row>
+    <row r="22" spans="1:21" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="28">
+        <v>8</v>
+      </c>
+      <c r="C22" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="22">
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="31"/>
+      <c r="I22" s="28">
+        <v>8</v>
+      </c>
+      <c r="J22" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="87"/>
+      <c r="N22" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="O22" s="31"/>
+      <c r="P22" s="28">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="133"/>
+      <c r="R22" s="134"/>
+      <c r="S22" s="134"/>
+      <c r="T22" s="135"/>
+      <c r="U22" s="26"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="23">
         <v>6</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="22">
+      <c r="C23" s="94"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="23">
         <v>6</v>
       </c>
-      <c r="O11" s="64"/>
-      <c r="P11" s="65"/>
-      <c r="Q11" s="65"/>
-      <c r="R11" s="66"/>
-    </row>
-    <row r="12" spans="1:18" ht="54.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="J23" s="94"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="23">
+        <v>6</v>
+      </c>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="95"/>
+      <c r="S23" s="95"/>
+      <c r="T23" s="96"/>
+      <c r="U23" s="30"/>
+    </row>
+    <row r="24" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="25">
         <v>7</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24">
+      <c r="C24" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="33"/>
+      <c r="I24" s="25">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="24">
+      <c r="J24" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="87"/>
+      <c r="N24" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="O24" s="33"/>
+      <c r="P24" s="25">
         <v>7</v>
       </c>
-      <c r="O12" s="112" t="s">
-        <v>44</v>
-      </c>
-      <c r="P12" s="113"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="114"/>
-    </row>
-    <row r="13" spans="1:18" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="Q24" s="133"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134"/>
+      <c r="T24" s="135"/>
+      <c r="U24" s="26"/>
+    </row>
+    <row r="25" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="34"/>
+      <c r="B25" s="28">
         <v>8</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26">
+      <c r="C25" s="115" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="34"/>
+      <c r="I25" s="28">
         <v>8</v>
       </c>
-      <c r="I13" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="26">
+      <c r="J25" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="M25" s="87"/>
+      <c r="N25" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="O25" s="34"/>
+      <c r="P25" s="28">
         <v>8</v>
       </c>
-      <c r="O13" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="63"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="22">
-        <v>6</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="22">
-        <v>6</v>
-      </c>
-      <c r="I14" s="73"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="75"/>
-      <c r="M14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="22">
-        <v>6</v>
-      </c>
-      <c r="O14" s="73"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="75"/>
-    </row>
-    <row r="15" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24">
-        <v>7</v>
-      </c>
-      <c r="C15" s="61" t="s">
+      <c r="Q25" s="139" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" s="140"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="36">
+        <v>1</v>
+      </c>
+      <c r="C26" s="118" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="36">
+        <v>3</v>
+      </c>
+      <c r="J26" s="97"/>
+      <c r="K26" s="98"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="52"/>
+      <c r="O26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R26" s="98"/>
+      <c r="S26" s="98"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="52"/>
+    </row>
+    <row r="27" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="25">
+        <v>2</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="37"/>
+      <c r="I27" s="25">
+        <v>4</v>
+      </c>
+      <c r="J27" s="85" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="M27" s="87"/>
+      <c r="N27" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" s="37"/>
+      <c r="P27" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="133"/>
+      <c r="R27" s="134"/>
+      <c r="S27" s="134"/>
+      <c r="T27" s="135"/>
+      <c r="U27" s="41"/>
+    </row>
+    <row r="28" spans="1:21" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="38"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="121"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="28">
+        <v>5</v>
+      </c>
+      <c r="J28" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="105"/>
+      <c r="N28" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" s="38"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="130"/>
+      <c r="R28" s="131"/>
+      <c r="S28" s="131"/>
+      <c r="T28" s="132"/>
+      <c r="U28" s="42"/>
+    </row>
+    <row r="29" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="49"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="125"/>
+      <c r="E29" s="125"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="125"/>
+      <c r="L29" s="125"/>
+      <c r="M29" s="126"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="136"/>
+      <c r="R29" s="137"/>
+      <c r="S29" s="137"/>
+      <c r="T29" s="138"/>
+      <c r="U29" s="51"/>
+    </row>
+    <row r="30" spans="1:21" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="47"/>
+      <c r="B30" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24">
-        <v>7</v>
-      </c>
-      <c r="I15" s="70" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="24">
-        <v>7</v>
-      </c>
-      <c r="O15" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="63"/>
-    </row>
-    <row r="16" spans="1:18" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="28"/>
-      <c r="B16" s="26">
-        <v>8</v>
-      </c>
-      <c r="C16" s="76" t="s">
+      <c r="D30" s="101"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="H30" s="47"/>
+      <c r="I30" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="26">
-        <v>8</v>
-      </c>
-      <c r="I16" s="88" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="89"/>
-      <c r="K16" s="89"/>
-      <c r="L16" s="90"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="26">
-        <v>8</v>
-      </c>
-      <c r="O16" s="115"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="117"/>
-    </row>
-    <row r="17" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="22">
-        <v>6</v>
-      </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="22">
-        <v>6</v>
-      </c>
-      <c r="I17" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" s="92"/>
-      <c r="K17" s="92"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" s="22">
-        <v>6</v>
-      </c>
-      <c r="O17" s="94"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="96"/>
-    </row>
-    <row r="18" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
-        <v>7</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="24">
-        <v>7</v>
-      </c>
-      <c r="I18" s="70"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="24">
-        <v>7</v>
-      </c>
-      <c r="O18" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="63"/>
-    </row>
-    <row r="19" spans="1:18" ht="41.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="26">
-        <v>8</v>
-      </c>
-      <c r="C19" s="97" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="26">
-        <v>8</v>
-      </c>
-      <c r="I19" s="88"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="26">
-        <v>8</v>
-      </c>
-      <c r="O19" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="78"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="22">
-        <v>6</v>
-      </c>
-      <c r="C20" s="94"/>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="22">
-        <v>6</v>
-      </c>
-      <c r="I20" s="94"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="96"/>
-      <c r="M20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="22">
-        <v>6</v>
-      </c>
-      <c r="O20" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="84"/>
-    </row>
-    <row r="21" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>7</v>
-      </c>
-      <c r="C21" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24">
-        <v>7</v>
-      </c>
-      <c r="I21" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="24">
-        <v>7</v>
-      </c>
-      <c r="O21" s="118"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="120"/>
-    </row>
-    <row r="22" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="26">
-        <v>8</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="26">
-        <v>8</v>
-      </c>
-      <c r="I22" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="26">
-        <v>8</v>
-      </c>
-      <c r="O22" s="118"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="119"/>
-      <c r="R22" s="120"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="22">
-        <v>6</v>
-      </c>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="22">
-        <v>6</v>
-      </c>
-      <c r="I23" s="79"/>
-      <c r="J23" s="80"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="22">
-        <v>6</v>
-      </c>
-      <c r="O23" s="79"/>
-      <c r="P23" s="80"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="81"/>
-    </row>
-    <row r="24" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29"/>
-      <c r="B24" s="24">
-        <v>7</v>
-      </c>
-      <c r="C24" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="24">
-        <v>7</v>
-      </c>
-      <c r="I24" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="24">
-        <v>7</v>
-      </c>
-      <c r="O24" s="118"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="120"/>
-    </row>
-    <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="30"/>
-      <c r="B25" s="26">
-        <v>8</v>
-      </c>
-      <c r="C25" s="100" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="26">
-        <v>8</v>
-      </c>
-      <c r="I25" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="26">
-        <v>8</v>
-      </c>
-      <c r="O25" s="124" t="s">
-        <v>30</v>
-      </c>
-      <c r="P25" s="125"/>
-      <c r="Q25" s="125"/>
-      <c r="R25" s="126"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="32">
-        <v>1</v>
-      </c>
-      <c r="C26" s="103" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="32">
-        <v>3</v>
-      </c>
-      <c r="I26" s="82"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="32">
-        <v>1</v>
-      </c>
-      <c r="O26" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
-    </row>
-    <row r="27" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="24">
-        <v>2</v>
-      </c>
-      <c r="C27" s="61" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="24">
-        <v>4</v>
-      </c>
-      <c r="I27" s="70" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="24">
-        <v>2</v>
-      </c>
-      <c r="O27" s="118"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="119"/>
-      <c r="R27" s="120"/>
-    </row>
-    <row r="28" spans="1:18" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="26">
-        <v>5</v>
-      </c>
-      <c r="I28" s="88" t="s">
-        <v>77</v>
-      </c>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="117"/>
-    </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="42"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="109"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="109"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="110"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="121"/>
-      <c r="P29" s="122"/>
-      <c r="Q29" s="122"/>
-      <c r="R29" s="123"/>
-    </row>
-    <row r="30" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="85" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="I30" s="85" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="40"/>
-      <c r="N30" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="O30" s="85" t="s">
-        <v>34</v>
-      </c>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="86"/>
-      <c r="R30" s="87"/>
-    </row>
-    <row r="31" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="37"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="39"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="39"/>
-      <c r="R31" s="39"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="J30" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" s="101"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="102"/>
+      <c r="N30" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="O30" s="47"/>
+      <c r="P30" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q30" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="R30" s="101"/>
+      <c r="S30" s="101"/>
+      <c r="T30" s="102"/>
+      <c r="U30" s="54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="45"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="46"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="S32" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="2" t="s">
+      <c r="L33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q33" s="2" t="s">
-        <v>18</v>
+      <c r="S33" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O24:R24"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="O27:R27"/>
-    <mergeCell ref="O30:R30"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="Q14:T14"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="Q16:T16"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="Q11:T11"/>
+    <mergeCell ref="Q12:T12"/>
+    <mergeCell ref="Q13:T13"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
@@ -2635,57 +2935,57 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="J9:M9"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="3">
       <formula>IF($C$9=0,"",$C$9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
+  <conditionalFormatting sqref="J9">
     <cfRule type="expression" priority="2">
       <formula>IF($C$9=0,"",$C$9)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O9">
+  <conditionalFormatting sqref="Q9">
     <cfRule type="expression" priority="1">
       <formula>IF($C$9=0,"",$C$9)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 I7 O7"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 K6 Q6">
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 J7 Q7" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 L6 S6" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"осенний, весенний"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6 O6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 J6 Q6" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"2025-2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2695,8 +2995,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2705,96 +3005,99 @@
     <col min="4" max="4" width="17.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="20" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="16.140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="17.5703125" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="20" style="2" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="16.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.140625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="H2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="O2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="L4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="1"/>
-      <c r="R4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="M4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="T4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -2803,889 +3106,981 @@
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="4" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="7"/>
+      <c r="O5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="6"/>
+      <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="7"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="R5" s="6"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="7"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="J6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="L6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="O6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" s="11" t="s">
+      <c r="Q6" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="R6" s="9"/>
+      <c r="S6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="35"/>
+      <c r="C7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="39"/>
       <c r="E7" s="10">
         <v>2</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="10">
+      <c r="J7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="39"/>
+      <c r="L7" s="10">
         <v>2</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="M7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="O7" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="10">
+      <c r="Q7" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="R7" s="39"/>
+      <c r="S7" s="10">
         <v>2</v>
       </c>
-      <c r="R7" s="11" t="s">
+      <c r="T7" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="47" t="s">
+    <row r="8" spans="1:21" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="62"/>
       <c r="E8" s="13" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="47" t="s">
+      <c r="H8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="47"/>
-      <c r="K8" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="14" t="s">
+      <c r="K8" s="62"/>
+      <c r="L8" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8" s="47" t="s">
+      <c r="O8" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="R8" s="14" t="s">
+      <c r="R8" s="62"/>
+      <c r="S8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="48" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-    </row>
-    <row r="10" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="H9" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="O9" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="63"/>
+      <c r="S9" s="63"/>
+      <c r="T9" s="63"/>
+    </row>
+    <row r="10" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="127" t="s">
+      <c r="C10" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="129"/>
-      <c r="G10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="16" t="s">
+      <c r="D10" s="143"/>
+      <c r="E10" s="143"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="J10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="J10" s="18"/>
       <c r="K10" s="19"/>
       <c r="L10" s="20"/>
-      <c r="M10" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="16" t="s">
+      <c r="M10" s="21"/>
+      <c r="N10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="O10" s="17" t="s">
+      <c r="Q10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="20"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="22">
+      <c r="R10" s="19"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="23">
         <v>6</v>
       </c>
-      <c r="C11" s="82"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="22">
+      <c r="C11" s="97"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="23">
         <v>6</v>
       </c>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="65"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="22">
+      <c r="J11" s="79"/>
+      <c r="K11" s="80"/>
+      <c r="L11" s="80"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="23">
         <v>6</v>
       </c>
-      <c r="O11" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="84"/>
-    </row>
-    <row r="12" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="Q11" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="99"/>
+      <c r="U11" s="30"/>
+    </row>
+    <row r="12" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>7</v>
       </c>
-      <c r="C12" s="112" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="114"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24">
+      <c r="C12" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="24"/>
+      <c r="I12" s="25">
         <v>7</v>
       </c>
-      <c r="I12" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="24">
+      <c r="J12" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="24"/>
+      <c r="P12" s="25">
         <v>7</v>
       </c>
-      <c r="O12" s="130"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="132"/>
-    </row>
-    <row r="13" spans="1:18" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="Q12" s="145"/>
+      <c r="R12" s="146"/>
+      <c r="S12" s="146"/>
+      <c r="T12" s="147"/>
+      <c r="U12" s="26"/>
+    </row>
+    <row r="13" spans="1:21" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28">
         <v>8</v>
       </c>
-      <c r="C13" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26">
+      <c r="C13" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28">
         <v>8</v>
       </c>
-      <c r="I13" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="26">
+      <c r="J13" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="87"/>
+      <c r="N13" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O13" s="27"/>
+      <c r="P13" s="28">
         <v>8</v>
       </c>
-      <c r="O13" s="133"/>
-      <c r="P13" s="134"/>
-      <c r="Q13" s="134"/>
-      <c r="R13" s="135"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="22">
+      <c r="Q13" s="148"/>
+      <c r="R13" s="149"/>
+      <c r="S13" s="149"/>
+      <c r="T13" s="150"/>
+      <c r="U13" s="26"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="23">
         <v>6</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="22">
+      <c r="C14" s="88"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="23">
         <v>6</v>
       </c>
-      <c r="I14" s="73"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="75"/>
-      <c r="M14" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="22">
+      <c r="J14" s="88"/>
+      <c r="K14" s="89"/>
+      <c r="L14" s="89"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" s="23">
         <v>6</v>
       </c>
-      <c r="O14" s="73"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="75"/>
-    </row>
-    <row r="15" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24">
+      <c r="Q14" s="88"/>
+      <c r="R14" s="89"/>
+      <c r="S14" s="89"/>
+      <c r="T14" s="90"/>
+      <c r="U14" s="30"/>
+    </row>
+    <row r="15" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
         <v>7</v>
       </c>
-      <c r="C15" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24">
+      <c r="C15" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25">
         <v>7</v>
       </c>
-      <c r="I15" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="24">
+      <c r="J15" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="87"/>
+      <c r="N15" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="25">
         <v>7</v>
       </c>
-      <c r="O15" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="63"/>
-    </row>
-    <row r="16" spans="1:18" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="28"/>
-      <c r="B16" s="26">
+      <c r="Q15" s="76" t="s">
+        <v>79</v>
+      </c>
+      <c r="R15" s="77"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="56" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="31"/>
+      <c r="B16" s="28">
         <v>8</v>
       </c>
-      <c r="C16" s="136"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="26">
+      <c r="C16" s="151"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="28">
         <v>8</v>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="26">
+      <c r="J16" s="130"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="132"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="28">
         <v>8</v>
       </c>
-      <c r="O16" s="115"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="117"/>
-    </row>
-    <row r="17" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="22">
+      <c r="Q16" s="130"/>
+      <c r="R16" s="131"/>
+      <c r="S16" s="131"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="32"/>
+    </row>
+    <row r="17" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="23">
         <v>6</v>
       </c>
-      <c r="C17" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="22">
+      <c r="C17" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="23">
         <v>6</v>
       </c>
-      <c r="I17" s="94"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="N17" s="22">
+      <c r="J17" s="109"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="23">
         <v>6</v>
       </c>
-      <c r="O17" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="P17" s="92"/>
-      <c r="Q17" s="92"/>
-      <c r="R17" s="93"/>
-    </row>
-    <row r="18" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
+      <c r="Q17" s="106" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="107"/>
+      <c r="S17" s="107"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="30"/>
+    </row>
+    <row r="18" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
         <v>7</v>
       </c>
-      <c r="C18" s="61"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="24">
+      <c r="C18" s="76"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="25">
         <v>7</v>
       </c>
-      <c r="I18" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="24">
+      <c r="J18" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" s="33"/>
+      <c r="P18" s="25">
         <v>7</v>
       </c>
-      <c r="O18" s="61"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="63"/>
-    </row>
-    <row r="19" spans="1:18" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="26">
+      <c r="Q18" s="76"/>
+      <c r="R18" s="77"/>
+      <c r="S18" s="77"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="56"/>
+    </row>
+    <row r="19" spans="1:21" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="31"/>
+      <c r="B19" s="28">
         <v>8</v>
       </c>
-      <c r="C19" s="97"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="26">
+      <c r="C19" s="112"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="28">
         <v>8</v>
       </c>
-      <c r="I19" s="88" t="s">
-        <v>68</v>
-      </c>
-      <c r="J19" s="89"/>
-      <c r="K19" s="89"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="26">
+      <c r="J19" s="103" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="105"/>
+      <c r="N19" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="O19" s="31"/>
+      <c r="P19" s="28">
         <v>8</v>
       </c>
-      <c r="O19" s="97"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="99"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="22">
+      <c r="Q19" s="112"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="113"/>
+      <c r="T19" s="114"/>
+      <c r="U19" s="56"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="23">
         <v>6</v>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="22">
+      <c r="C20" s="97"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="23">
         <v>6</v>
       </c>
-      <c r="I20" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="22">
+      <c r="J20" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="98"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="23">
         <v>6</v>
       </c>
-      <c r="O20" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="84"/>
-    </row>
-    <row r="21" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="Q20" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="99"/>
+      <c r="U20" s="30"/>
+    </row>
+    <row r="21" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>7</v>
       </c>
-      <c r="C21" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24">
+      <c r="C21" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="24"/>
+      <c r="I21" s="25">
         <v>7</v>
       </c>
-      <c r="I21" s="118"/>
-      <c r="J21" s="119"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="120"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="24">
+      <c r="J21" s="133"/>
+      <c r="K21" s="134"/>
+      <c r="L21" s="134"/>
+      <c r="M21" s="135"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="25">
         <v>7</v>
       </c>
-      <c r="O21" s="118"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="120"/>
-    </row>
-    <row r="22" spans="1:18" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="26">
+      <c r="Q21" s="133"/>
+      <c r="R21" s="134"/>
+      <c r="S21" s="134"/>
+      <c r="T21" s="135"/>
+      <c r="U21" s="26"/>
+    </row>
+    <row r="22" spans="1:21" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="28">
         <v>8</v>
       </c>
-      <c r="C22" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="26">
+      <c r="C22" s="112" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="31"/>
+      <c r="I22" s="28">
         <v>8</v>
       </c>
-      <c r="I22" s="118"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="120"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="26">
+      <c r="J22" s="133"/>
+      <c r="K22" s="134"/>
+      <c r="L22" s="134"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="28">
         <v>8</v>
       </c>
-      <c r="O22" s="118"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="119"/>
-      <c r="R22" s="120"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="22">
+      <c r="Q22" s="133"/>
+      <c r="R22" s="134"/>
+      <c r="S22" s="134"/>
+      <c r="T22" s="135"/>
+      <c r="U22" s="26"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="23">
         <v>6</v>
       </c>
-      <c r="C23" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="22">
+      <c r="C23" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="23">
         <v>6</v>
       </c>
-      <c r="I23" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="84"/>
-      <c r="M23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="22">
+      <c r="J23" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" s="98"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" s="23">
         <v>6</v>
       </c>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
-    </row>
-    <row r="24" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29"/>
-      <c r="B24" s="24">
+      <c r="Q23" s="97"/>
+      <c r="R23" s="98"/>
+      <c r="S23" s="98"/>
+      <c r="T23" s="99"/>
+      <c r="U23" s="30"/>
+    </row>
+    <row r="24" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="25">
         <v>7</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="24">
+      <c r="C24" s="133"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="25">
         <v>7</v>
       </c>
-      <c r="I24" s="118"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="120"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="24">
+      <c r="J24" s="133"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="135"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="25">
         <v>7</v>
       </c>
-      <c r="O24" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="63"/>
-    </row>
-    <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="30"/>
-      <c r="B25" s="26">
+      <c r="Q24" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="R24" s="77"/>
+      <c r="S24" s="77"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="34"/>
+      <c r="B25" s="28">
         <v>8</v>
       </c>
-      <c r="C25" s="118"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="26">
+      <c r="C25" s="133"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="28">
         <v>8</v>
       </c>
-      <c r="I25" s="118"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="119"/>
-      <c r="L25" s="120"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="26">
+      <c r="J25" s="133"/>
+      <c r="K25" s="134"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="135"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="28">
         <v>8</v>
       </c>
-      <c r="O25" s="97" t="s">
-        <v>66</v>
-      </c>
-      <c r="P25" s="98"/>
-      <c r="Q25" s="98"/>
-      <c r="R25" s="99"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="32">
+      <c r="Q25" s="112" t="s">
+        <v>78</v>
+      </c>
+      <c r="R25" s="113"/>
+      <c r="S25" s="113"/>
+      <c r="T25" s="114"/>
+      <c r="U25" s="56" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="36">
         <v>1</v>
       </c>
-      <c r="C26" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="32">
+      <c r="C26" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="36">
         <v>1</v>
       </c>
-      <c r="I26" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="84"/>
-      <c r="M26" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="32">
+      <c r="J26" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="98"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="99"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="36">
         <v>1</v>
       </c>
-      <c r="O26" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="24">
+      <c r="Q26" s="97" t="s">
+        <v>50</v>
+      </c>
+      <c r="R26" s="98"/>
+      <c r="S26" s="98"/>
+      <c r="T26" s="99"/>
+      <c r="U26" s="53"/>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="37"/>
+      <c r="B27" s="25">
         <v>2</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="24">
+      <c r="C27" s="133"/>
+      <c r="D27" s="134"/>
+      <c r="E27" s="134"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="25">
         <v>2</v>
       </c>
-      <c r="I27" s="118"/>
-      <c r="J27" s="119"/>
-      <c r="K27" s="119"/>
-      <c r="L27" s="120"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="24">
+      <c r="J27" s="133"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="134"/>
+      <c r="M27" s="135"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="25">
         <v>2</v>
       </c>
-      <c r="O27" s="118"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="119"/>
-      <c r="R27" s="120"/>
-    </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="106"/>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="117"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="117"/>
-    </row>
-    <row r="29" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="39"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="Q27" s="133"/>
+      <c r="R27" s="134"/>
+      <c r="S27" s="134"/>
+      <c r="T27" s="135"/>
+      <c r="U27" s="41"/>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="38"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="121"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="132"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="130"/>
+      <c r="R28" s="131"/>
+      <c r="S28" s="131"/>
+      <c r="T28" s="132"/>
+      <c r="U28" s="42"/>
+    </row>
+    <row r="29" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="46"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.4">
       <c r="B30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="S30" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N31" s="2" t="s">
+      <c r="L31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>18</v>
+      <c r="S31" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="61">
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="O27:R27"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="Q27:T27"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="Q28:T28"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="O25:R25"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="Q25:T25"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="O26:R26"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="Q26:T26"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="Q23:T23"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="O24:R24"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="Q24:T24"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="Q21:T21"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="Q22:T22"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="Q19:T19"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="Q20:T20"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="Q17:T17"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="Q18:T18"/>
     <mergeCell ref="C15:F15"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="Q15:T15"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="Q16:T16"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="Q13:T13"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="Q14:T14"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="Q11:T11"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="Q12:T12"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="Q8:R8"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="Q9:T9"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 I6 O6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6 J6 Q6" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"2025-2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 K6 Q6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6 L6 S6" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"осенний, весенний"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 I7 O7"/>
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7 J7 Q7" xr:uid="{00000000-0002-0000-0100-000002000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3704,14 +4099,14 @@
             <xm:f>IF('1 курс'!$C$9=0,"",'1 курс'!$C$9)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>I9</xm:sqref>
+          <xm:sqref>J9</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="1" id="{9A4C594C-135A-422D-BEEE-6BC2BCB798E2}">
             <xm:f>IF('1 курс'!$C$9=0,"",'1 курс'!$C$9)</xm:f>
             <x14:dxf/>
           </x14:cfRule>
-          <xm:sqref>O9</xm:sqref>
+          <xm:sqref>Q9</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
